--- a/6-docs/9-PinDefine/引脚定义.xlsx
+++ b/6-docs/9-PinDefine/引脚定义.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project_HITZRI\26-02-24_PipelineRobot\9-PinDefine\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project_HITZRI\26-02-24_PipelineRobot\6-docs\9-PinDefine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766A453F-43D5-4B93-B49A-732868E0F861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE249FC-7F83-427A-83C2-2A188E93657C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51090" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{C380D3C2-AED4-45C9-B2E3-250A201696C1}"/>
+    <workbookView xWindow="50205" yWindow="2205" windowWidth="21600" windowHeight="11055" xr2:uid="{C380D3C2-AED4-45C9-B2E3-250A201696C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -136,7 +136,29 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>液体传感器输出信号</t>
+    <t>GPIO43</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO44</t>
+  </si>
+  <si>
+    <t>UART0 TX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UART0 RX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>液体传感器输输入信号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO39</t>
+  </si>
+  <si>
+    <t>声呐通电信号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -507,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC24CF5-C5E9-4319-9ABA-8C22A330DC36}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="3" width="9.06640625" style="2"/>
@@ -655,8 +677,47 @@
       <c r="B11" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="C11" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A14" s="2">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/6-docs/9-PinDefine/引脚定义.xlsx
+++ b/6-docs/9-PinDefine/引脚定义.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project_HITZRI\26-02-24_PipelineRobot\6-docs\9-PinDefine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE249FC-7F83-427A-83C2-2A188E93657C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3F7B94-3783-420B-8051-4F45A5F08DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="50205" yWindow="2205" windowWidth="21600" windowHeight="11055" xr2:uid="{C380D3C2-AED4-45C9-B2E3-250A201696C1}"/>
+    <workbookView xWindow="55260" yWindow="2745" windowWidth="21600" windowHeight="11055" xr2:uid="{C380D3C2-AED4-45C9-B2E3-250A201696C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -159,6 +159,18 @@
   </si>
   <si>
     <t>声呐通电信号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编码器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上位机控制话题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给算法端的话题</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -529,14 +541,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC24CF5-C5E9-4319-9ABA-8C22A330DC36}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="3" width="9.06640625" style="2"/>
     <col min="4" max="4" width="65" customWidth="1"/>
+    <col min="6" max="6" width="16.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -550,7 +563,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="27.75" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -564,7 +577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -578,7 +591,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -592,7 +605,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -606,7 +619,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -620,7 +633,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -634,7 +647,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -648,7 +661,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -659,7 +672,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -670,7 +683,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -684,7 +697,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -698,7 +711,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -709,7 +722,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -718,6 +731,21 @@
       </c>
       <c r="D14" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.4">
+      <c r="F17" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/6-docs/9-PinDefine/引脚定义.xlsx
+++ b/6-docs/9-PinDefine/引脚定义.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project_HITZRI\26-02-24_PipelineRobot\6-docs\9-PinDefine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3F7B94-3783-420B-8051-4F45A5F08DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FDFB865-1562-4D41-BEA0-ADB25CC37C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="55260" yWindow="2745" windowWidth="21600" windowHeight="11055" xr2:uid="{C380D3C2-AED4-45C9-B2E3-250A201696C1}"/>
+    <workbookView xWindow="1283" yWindow="1357" windowWidth="21600" windowHeight="11056" xr2:uid="{C380D3C2-AED4-45C9-B2E3-250A201696C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,10 +55,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>GPIO0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GPIO1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -171,6 +167,10 @@
   </si>
   <si>
     <t>给算法端的话题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -568,13 +568,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -582,13 +582,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
@@ -596,13 +596,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -610,13 +610,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
@@ -624,13 +624,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
@@ -638,13 +638,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
@@ -652,13 +652,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
         <v>18</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
@@ -666,10 +666,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
@@ -677,10 +677,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
@@ -688,13 +688,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
@@ -702,13 +702,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
         <v>30</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
@@ -716,10 +716,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
@@ -727,25 +727,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="F15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="F16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/6-docs/9-PinDefine/引脚定义.xlsx
+++ b/6-docs/9-PinDefine/引脚定义.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project_HITZRI\26-02-24_PipelineRobot\6-docs\9-PinDefine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FDFB865-1562-4D41-BEA0-ADB25CC37C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E746F516-6471-4B68-B92B-D4F6A5253089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1283" yWindow="1357" windowWidth="21600" windowHeight="11056" xr2:uid="{C380D3C2-AED4-45C9-B2E3-250A201696C1}"/>
+    <workbookView xWindow="47880" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C380D3C2-AED4-45C9-B2E3-250A201696C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -158,19 +158,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>编码器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>上位机控制话题</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>给算法端的话题</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GPIO15</t>
+    <t>`</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COM2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>接声呐供电</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -541,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC24CF5-C5E9-4319-9ABA-8C22A330DC36}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="3" width="9.06640625" style="2"/>
@@ -549,7 +549,7 @@
     <col min="6" max="6" width="16.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -563,12 +563,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
@@ -577,7 +577,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -591,7 +591,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -605,7 +605,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -619,7 +619,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -633,7 +633,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -647,7 +647,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -661,7 +661,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -672,7 +672,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -683,7 +683,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -697,7 +697,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -711,7 +711,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -722,7 +722,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -733,18 +733,16 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="F15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="F16" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B16" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.4">
-      <c r="F17" t="s">
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B17" s="2" t="s">
         <v>33</v>
       </c>
     </row>
